--- a/backend/templates/fp-analysis/fp_database_template.xlsx
+++ b/backend/templates/fp-analysis/fp_database_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\khize\Study_Material\Projects\EY\Governance_Platform\backend\templates\fp-analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4DFA25-5FF0-4D28-ABC6-4A904FD8BB0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A2F88B-6E5C-46A8-9173-5C27A568ECC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="29">
   <si>
     <t>PRIVILEGE_DISPLAY_NAME</t>
   </si>
@@ -63,9 +63,6 @@
     <t>The gatekeeper privilege a user must hold to access the work area.  Example: 'Access Payables Work Area'</t>
   </si>
   <si>
-    <t>A privilege that becomes a FP if the user also holds the gatekeeper privilege above.  Example: 'Manage Payables Invoices'</t>
-  </si>
-  <si>
     <t>Rules &amp; Validation</t>
   </si>
   <si>
@@ -75,18 +72,9 @@
     <t>'FALSE POSITIVE REASON' uses a space — not an underscore.</t>
   </si>
   <si>
-    <t>Empty sheets OK:</t>
-  </si>
-  <si>
-    <t>Both sheets can be header-only if your ruleset has no entries.</t>
-  </si>
-  <si>
     <t>Entitlement mode:</t>
   </si>
   <si>
-    <t>In Entitlement mode replace PRIVILEGE_DISPLAY_NAME with ENTITLEMENT in WorkArea_Privileges.</t>
-  </si>
-  <si>
     <t>Do's and Don'ts</t>
   </si>
   <si>
@@ -109,6 +97,18 @@
   </si>
   <si>
     <t>Both sheets must be present</t>
+  </si>
+  <si>
+    <t>A privilege that becomes a FP if the user does not holds the gatekeeper privilege above.  Example: 'Manage Payables Invoices'</t>
+  </si>
+  <si>
+    <t>In Entitlement mode replace PRIVILEGE_DISPLAY_NAME with ENTITLEMENT in WorkArea_Privileges sheet.</t>
+  </si>
+  <si>
+    <t>Update column names.</t>
+  </si>
+  <si>
+    <t>Update sheet names.</t>
   </si>
 </sst>
 </file>
@@ -203,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -214,12 +214,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -566,7 +569,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -578,258 +581,260 @@
       <c r="A1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="15" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="15" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="19" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="B20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-    </row>
-    <row r="20" spans="1:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+        <v>27</v>
+      </c>
     </row>
     <row r="23" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+        <v>28</v>
+      </c>
     </row>
     <row r="24" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B24:G24"/>
+  <mergeCells count="18">
+    <mergeCell ref="B9:G9"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="B25:G25"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="B4:G4"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="B12:G12"/>
-    <mergeCell ref="B18:G18"/>
-    <mergeCell ref="B21:G21"/>
     <mergeCell ref="B17:G17"/>
-    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="B8:G8"/>
-    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="B13:G13"/>
-    <mergeCell ref="B9:G9"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A11:G11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
